--- a/data/trans_orig/P04B1_2_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P04B1_2_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su vivienda tiene una temperatura suficientemente fresca durante el verano en 2023</t>
+          <t>Población según si su vivienda tiene una temperatura suficientemente fresca durante el verano en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>277550</t>
+          <t>279197</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>318968</t>
+          <t>320241</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>397643</t>
+          <t>398484</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>440166</t>
+          <t>436329</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>689176</t>
+          <t>685621</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>748724</t>
+          <t>748597</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,92%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>195970</t>
+          <t>194697</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>237388</t>
+          <t>235741</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>315342</t>
+          <t>319179</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>357865</t>
+          <t>357024</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>521722</t>
+          <t>521849</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>581270</t>
+          <t>584825</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>46,03%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1467873</t>
+          <t>1468850</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1782567</t>
+          <t>1821761</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1441657</t>
+          <t>1444179</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1726718</t>
+          <t>1710909</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2948516</t>
+          <t>2951785</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3393643</t>
+          <t>3392693</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,99%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>504778</t>
+          <t>465584</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>819472</t>
+          <t>818495</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>509844</t>
+          <t>525653</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>794905</t>
+          <t>792383</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1130264</t>
+          <t>1131214</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1575391</t>
+          <t>1572122</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,75%</t>
         </is>
       </c>
     </row>
@@ -1411,17 +1411,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>439013</t>
+          <t>439014</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>414919</t>
+          <t>414493</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>462893</t>
+          <t>464948</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>440454</t>
+          <t>438944</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>480549</t>
+          <t>480563</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>866297</t>
+          <t>865182</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>928263</t>
+          <t>930977</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,42%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>181682</t>
+          <t>179628</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>229656</t>
+          <t>230083</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>178367</t>
+          <t>178353</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>218462</t>
+          <t>219972</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>375228</t>
+          <t>372514</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>437194</t>
+          <t>438309</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,63%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>644575</t>
+          <t>644576</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>644575</t>
+          <t>644576</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>644575</t>
+          <t>644576</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2201237</t>
+          <t>2204869</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2562734</t>
+          <t>2564705</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2317577</t>
+          <t>2316095</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2639918</t>
+          <t>2656909</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4570248</t>
+          <t>4567937</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5056862</t>
+          <t>5027128</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>70,83%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>884125</t>
+          <t>882154</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1245622</t>
+          <t>1241990</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1011067</t>
+          <t>994076</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1333408</t>
+          <t>1334890</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2040982</t>
+          <t>2070716</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2527596</t>
+          <t>2529907</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,64%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04B1_2_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P04B1_2_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>299763</t>
+          <t>334216</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>279197</t>
+          <t>310528</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>320241</t>
+          <t>356570</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>417780</t>
+          <t>441256</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>398484</t>
+          <t>418608</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>436329</t>
+          <t>465274</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>717543</t>
+          <t>775472</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>685621</t>
+          <t>741040</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>748597</t>
+          <t>806371</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>57,57%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>215175</t>
+          <t>244313</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>194697</t>
+          <t>221959</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>235741</t>
+          <t>268001</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>337728</t>
+          <t>380782</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>319179</t>
+          <t>356764</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>357024</t>
+          <t>403430</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>552903</t>
+          <t>625095</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>521849</t>
+          <t>594196</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>584825</t>
+          <t>659527</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>47,09%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1574120</t>
+          <t>1406186</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1468850</t>
+          <t>1355312</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1821761</t>
+          <t>1460114</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1542392</t>
+          <t>1367044</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1444179</t>
+          <t>1326961</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1710909</t>
+          <t>1407847</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3116512</t>
+          <t>2773230</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2951785</t>
+          <t>2706647</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3392693</t>
+          <t>2836505</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>64,51%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>713225</t>
+          <t>821127</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>465584</t>
+          <t>767199</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>818495</t>
+          <t>872001</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>694170</t>
+          <t>802962</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>525653</t>
+          <t>762159</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>792383</t>
+          <t>843045</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1407395</t>
+          <t>1624089</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1131214</t>
+          <t>1560814</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1572122</t>
+          <t>1690672</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>38,45%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2287345</t>
+          <t>2227313</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2287345</t>
+          <t>2227313</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2287345</t>
+          <t>2227313</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2236562</t>
+          <t>2170006</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2236562</t>
+          <t>2170006</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2236562</t>
+          <t>2170006</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4523907</t>
+          <t>4397319</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4523907</t>
+          <t>4397319</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4523907</t>
+          <t>4397319</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>439014</t>
+          <t>472242</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>414493</t>
+          <t>444718</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>464948</t>
+          <t>496691</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>460940</t>
+          <t>502341</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>438944</t>
+          <t>479992</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>480563</t>
+          <t>524389</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>899953</t>
+          <t>974583</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>865182</t>
+          <t>938504</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>930977</t>
+          <t>1011569</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>70,22%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>205562</t>
+          <t>235885</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>179628</t>
+          <t>211436</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>230083</t>
+          <t>263409</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>197976</t>
+          <t>230115</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>178353</t>
+          <t>208067</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>219972</t>
+          <t>252464</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>403538</t>
+          <t>466000</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>372514</t>
+          <t>429014</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>438309</t>
+          <t>502079</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>34,85%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>644576</t>
+          <t>708127</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>644576</t>
+          <t>708127</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>644576</t>
+          <t>708127</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>658916</t>
+          <t>732456</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>658916</t>
+          <t>732456</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>658916</t>
+          <t>732456</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1303491</t>
+          <t>1440583</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1303491</t>
+          <t>1440583</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1303491</t>
+          <t>1440583</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2312896</t>
+          <t>2212644</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2204869</t>
+          <t>2151256</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2564705</t>
+          <t>2279981</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2421111</t>
+          <t>2310641</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2316095</t>
+          <t>2255783</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2656909</t>
+          <t>2364238</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4734007</t>
+          <t>4523285</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4567937</t>
+          <t>4445758</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5027128</t>
+          <t>4598841</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>63,53%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1133963</t>
+          <t>1301326</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>882154</t>
+          <t>1233989</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1241990</t>
+          <t>1362714</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1229874</t>
+          <t>1413859</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>994076</t>
+          <t>1360262</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1334890</t>
+          <t>1468717</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2363837</t>
+          <t>2715185</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2070716</t>
+          <t>2639629</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2529907</t>
+          <t>2792712</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>38,58%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3446859</t>
+          <t>3513970</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3446859</t>
+          <t>3513970</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3446859</t>
+          <t>3513970</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3650985</t>
+          <t>3724500</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3650985</t>
+          <t>3724500</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3650985</t>
+          <t>3724500</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7097844</t>
+          <t>7238470</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7097844</t>
+          <t>7238470</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7097844</t>
+          <t>7238470</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
